--- a/data/User_Master.xlsx
+++ b/data/User_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://apparelme-my.sharepoint.com/personal/138925_appareluae_com/Documents/F&amp;B Sales Dashboard - Project/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="8_{435EB669-0B53-404B-9887-A50634BD41E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{652C854E-E07B-4B04-9021-69BC9B9B429A}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="8_{435EB669-0B53-404B-9887-A50634BD41E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3CFE486B-DAD5-4D99-9CC0-E254A711A119}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{B76173A0-443A-4532-A0AF-4EB7DE1D271E}"/>
+    <workbookView xWindow="9410" yWindow="4200" windowWidth="11760" windowHeight="6160" xr2:uid="{B76173A0-443A-4532-A0AF-4EB7DE1D271E}"/>
   </bookViews>
   <sheets>
     <sheet name="Employee_Master_tbl" sheetId="1" r:id="rId1"/>
@@ -51,19 +51,19 @@
     <t>User</t>
   </si>
   <si>
-    <t>IsActive</t>
-  </si>
-  <si>
-    <t>Emp_ID</t>
-  </si>
-  <si>
-    <t>Password</t>
-  </si>
-  <si>
-    <t>Role</t>
-  </si>
-  <si>
-    <t>Last_Login</t>
+    <t>emp_id</t>
+  </si>
+  <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>role</t>
+  </si>
+  <si>
+    <t>is_active</t>
+  </si>
+  <si>
+    <t>last_login</t>
   </si>
 </sst>
 </file>
@@ -430,16 +430,16 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>7</v>
